--- a/5/search/FY2_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,75 +492,75 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>278.2</v>
+        <v>292.8</v>
       </c>
       <c r="B2" t="n">
-        <v>139.5</v>
+        <v>127.6</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>12075.60759775729</v>
+        <v>12306.57133075399</v>
       </c>
       <c r="F2" t="n">
-        <v>875.3196199957811</v>
+        <v>670.6956235153054</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12139.27715376343</v>
+        <v>12405.46530841656</v>
       </c>
       <c r="I2" t="n">
-        <v>433.4835105185441</v>
+        <v>435.4361472299203</v>
       </c>
       <c r="J2" t="n">
-        <v>1349.824</v>
+        <v>1380.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.000000000000001</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>299.4</v>
+        <v>297</v>
       </c>
       <c r="B3" t="n">
-        <v>90.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>12.2</v>
+        <v>9.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
-        <v>12544.40244468412</v>
+        <v>12424.49927687647</v>
       </c>
       <c r="F3" t="n">
-        <v>433.8413077439322</v>
+        <v>566.8732596229083</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>12553.32707492484</v>
+        <v>12495.24915635588</v>
       </c>
       <c r="I3" t="n">
-        <v>418.0026406577672</v>
+        <v>428.0188028933931</v>
       </c>
       <c r="J3" t="n">
-        <v>1399.804</v>
+        <v>1387.456</v>
       </c>
       <c r="K3" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>29</v>
@@ -568,306 +568,306 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>299.4</v>
+        <v>294.4</v>
       </c>
       <c r="B4" t="n">
-        <v>91.90000000000001</v>
+        <v>132.6</v>
       </c>
       <c r="C4" t="n">
-        <v>11.8</v>
+        <v>6.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
-        <v>12532.34584849533</v>
+        <v>12339.62141384735</v>
       </c>
       <c r="F4" t="n">
-        <v>455.2383189450441</v>
+        <v>651.3087487780257</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12550.39147047822</v>
+        <v>12438.22117915787</v>
       </c>
       <c r="I4" t="n">
-        <v>423.2124992482659</v>
+        <v>433.9467726168074</v>
       </c>
       <c r="J4" t="n">
-        <v>1399.216</v>
+        <v>1384.124</v>
       </c>
       <c r="K4" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>297.8</v>
+        <v>291.2</v>
       </c>
       <c r="B5" t="n">
-        <v>93.90000000000001</v>
+        <v>126.6</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>12481.73076080707</v>
+        <v>12283.84635754883</v>
       </c>
       <c r="F5" t="n">
-        <v>486.3163107003396</v>
+        <v>668.2004019499201</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12516.76572522941</v>
+        <v>12375.40969869362</v>
       </c>
       <c r="I5" t="n">
-        <v>419.8665878421824</v>
+        <v>432.1360154821525</v>
       </c>
       <c r="J5" t="n">
-        <v>1396.864</v>
+        <v>1380.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>276.6</v>
+        <v>289.6</v>
       </c>
       <c r="B6" t="n">
-        <v>139</v>
+        <v>135.6</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>12060.70980289033</v>
+        <v>12254.72850400555</v>
       </c>
       <c r="F6" t="n">
-        <v>875.3005052098706</v>
+        <v>684.6392526514386</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>12111.83384742956</v>
+        <v>12345.70296972182</v>
       </c>
       <c r="I6" t="n">
-        <v>433.4482990708143</v>
+        <v>429.1532714555238</v>
       </c>
       <c r="J6" t="n">
-        <v>1349.824</v>
+        <v>1380.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.900000000000001</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254.4</v>
+        <v>296</v>
       </c>
       <c r="B7" t="n">
-        <v>134.1</v>
+        <v>127.6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="E7" t="n">
-        <v>11877.38869698868</v>
+        <v>12380.36587664595</v>
       </c>
       <c r="F7" t="n">
-        <v>960.8556592942758</v>
+        <v>620.1343819071388</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11725.92767562175</v>
+        <v>12469.8637299744</v>
       </c>
       <c r="I7" t="n">
-        <v>418.3832384224989</v>
+        <v>436.6365894147009</v>
       </c>
       <c r="J7" t="n">
-        <v>1313.564</v>
+        <v>1387.456</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>299.4</v>
+        <v>277.4</v>
       </c>
       <c r="B8" t="n">
-        <v>91.90000000000001</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>11.4</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>12514.30022651244</v>
+        <v>12072.12553408344</v>
       </c>
       <c r="F8" t="n">
-        <v>487.2641386418222</v>
+        <v>844.6641490654694</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>12550.39147047822</v>
+        <v>12126.21968464601</v>
       </c>
       <c r="I8" t="n">
-        <v>423.2124992482658</v>
+        <v>428.1622608645714</v>
       </c>
       <c r="J8" t="n">
-        <v>1396.864</v>
+        <v>1355.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>285.6</v>
+        <v>295.4</v>
       </c>
       <c r="B9" t="n">
-        <v>105.1</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
-        <v>12197.84431202665</v>
+        <v>12396.95372985661</v>
       </c>
       <c r="F9" t="n">
-        <v>691.4012996069631</v>
+        <v>564.0173865725868</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>12271.32934220798</v>
+        <v>12463.11268483271</v>
       </c>
       <c r="I9" t="n">
-        <v>428.2074966038351</v>
+        <v>424.6869510013513</v>
       </c>
       <c r="J9" t="n">
-        <v>1366.876</v>
+        <v>1387.456</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.999999999999998</v>
       </c>
       <c r="L9" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="B10" t="n">
-        <v>92.90000000000001</v>
+        <v>132.6</v>
       </c>
       <c r="C10" t="n">
-        <v>11.8</v>
+        <v>6.2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
-        <v>12564.5950384779</v>
+        <v>12254.04905141553</v>
       </c>
       <c r="F10" t="n">
-        <v>460.3560616243303</v>
+        <v>618.1174168234284</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>12583.73385334156</v>
+        <v>12319.61009694212</v>
       </c>
       <c r="I10" t="n">
-        <v>428.5037247302398</v>
+        <v>416.3412663262485</v>
       </c>
       <c r="J10" t="n">
-        <v>1399.216</v>
+        <v>1387.456</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B11" t="n">
-        <v>105.1</v>
+        <v>135.6</v>
       </c>
       <c r="C11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>12322.8434543377</v>
+        <v>12475.54502003679</v>
       </c>
       <c r="F11" t="n">
-        <v>600.9344104572514</v>
+        <v>424.9882185746636</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>12393.71152968012</v>
+        <v>12475.54502003679</v>
       </c>
       <c r="I11" t="n">
-        <v>425.5297688503065</v>
+        <v>424.9882185746636</v>
       </c>
       <c r="J11" t="n">
-        <v>1384.124</v>
+        <v>1400</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.900000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY2_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY2_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,382 +492,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>292.8</v>
+        <v>262.3</v>
       </c>
       <c r="B2" t="n">
-        <v>127.6</v>
+        <v>123</v>
       </c>
       <c r="C2" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>12306.57133075399</v>
+        <v>11934.0787967742</v>
       </c>
       <c r="F2" t="n">
-        <v>670.6956235153054</v>
+        <v>912.4362657403005</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12405.46530841656</v>
+        <v>11868.1575935484</v>
       </c>
       <c r="I2" t="n">
-        <v>435.4361472299203</v>
+        <v>424.8725314806011</v>
       </c>
       <c r="J2" t="n">
-        <v>1380.4</v>
+        <v>1321.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.000000000000002</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>297</v>
+        <v>275.8</v>
       </c>
       <c r="B3" t="n">
-        <v>97.40000000000001</v>
+        <v>139.4</v>
       </c>
       <c r="C3" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="E3" t="n">
-        <v>12424.49927687647</v>
+        <v>12053.53154174375</v>
       </c>
       <c r="F3" t="n">
-        <v>566.8732596229083</v>
+        <v>872.9917909192143</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>12495.24915635588</v>
+        <v>12098.61073479112</v>
       </c>
       <c r="I3" t="n">
-        <v>428.0188028933931</v>
+        <v>429.1954043248684</v>
       </c>
       <c r="J3" t="n">
-        <v>1387.456</v>
+        <v>1349.824</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.000000000000002</v>
       </c>
       <c r="L3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>294.4</v>
+        <v>278.2</v>
       </c>
       <c r="B4" t="n">
-        <v>132.6</v>
+        <v>139.4</v>
       </c>
       <c r="C4" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="E4" t="n">
-        <v>12339.62141384735</v>
+        <v>12075.55339876248</v>
       </c>
       <c r="F4" t="n">
-        <v>651.3087487780257</v>
+        <v>875.695734963526</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12438.22117915787</v>
+        <v>12139.17731350984</v>
       </c>
       <c r="I4" t="n">
-        <v>433.9467726168074</v>
+        <v>434.1763538801794</v>
       </c>
       <c r="J4" t="n">
-        <v>1384.124</v>
+        <v>1349.824</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>291.2</v>
+        <v>278.2</v>
       </c>
       <c r="B5" t="n">
-        <v>126.6</v>
+        <v>139.5</v>
       </c>
       <c r="C5" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E5" t="n">
-        <v>12283.84635754883</v>
+        <v>12075.60759775729</v>
       </c>
       <c r="F5" t="n">
-        <v>668.2004019499201</v>
+        <v>875.3196199957811</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12375.40969869362</v>
+        <v>12139.27715376343</v>
       </c>
       <c r="I5" t="n">
-        <v>432.1360154821525</v>
+        <v>433.4835105185441</v>
       </c>
       <c r="J5" t="n">
-        <v>1380.4</v>
+        <v>1349.824</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>289.6</v>
+        <v>277.4</v>
       </c>
       <c r="B6" t="n">
-        <v>135.6</v>
+        <v>139.4</v>
       </c>
       <c r="C6" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="E6" t="n">
-        <v>12254.72850400555</v>
+        <v>12068.22560341907</v>
       </c>
       <c r="F6" t="n">
-        <v>684.6392526514386</v>
+        <v>874.6919518624293</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>12345.70296972182</v>
+        <v>12125.67874314039</v>
       </c>
       <c r="I6" t="n">
-        <v>429.1532714555238</v>
+        <v>432.3272797465802</v>
       </c>
       <c r="J6" t="n">
-        <v>1380.4</v>
+        <v>1349.824</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>296</v>
+        <v>275.8</v>
       </c>
       <c r="B7" t="n">
-        <v>127.6</v>
+        <v>139.3</v>
       </c>
       <c r="C7" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="E7" t="n">
-        <v>12380.36587664595</v>
+        <v>12053.49314035082</v>
       </c>
       <c r="F7" t="n">
-        <v>620.1343819071388</v>
+        <v>873.3698455885692</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>12469.8637299744</v>
+        <v>12098.53999538309</v>
       </c>
       <c r="I7" t="n">
-        <v>436.6365894147009</v>
+        <v>429.8918208210485</v>
       </c>
       <c r="J7" t="n">
-        <v>1387.456</v>
+        <v>1349.824</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>277.4</v>
+        <v>276.6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>139.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E8" t="n">
-        <v>12072.12553408344</v>
+        <v>12060.84083124189</v>
       </c>
       <c r="F8" t="n">
-        <v>844.6641490654694</v>
+        <v>874.1680602570862</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>12126.21968464601</v>
+        <v>12112.07521544559</v>
       </c>
       <c r="I8" t="n">
-        <v>428.1622608645714</v>
+        <v>431.3622162630534</v>
       </c>
       <c r="J8" t="n">
-        <v>1355.9</v>
+        <v>1349.824</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>295.4</v>
+        <v>275</v>
       </c>
       <c r="B9" t="n">
-        <v>96.40000000000001</v>
+        <v>139.3</v>
       </c>
       <c r="C9" t="n">
-        <v>9.6</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="E9" t="n">
-        <v>12396.95372985661</v>
+        <v>12046.13502086605</v>
       </c>
       <c r="F9" t="n">
-        <v>564.0173865725868</v>
+        <v>872.6742985121153</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>12463.11268483271</v>
+        <v>12084.98556475324</v>
       </c>
       <c r="I9" t="n">
-        <v>424.6869510013513</v>
+        <v>428.6105498907388</v>
       </c>
       <c r="J9" t="n">
-        <v>1387.456</v>
+        <v>1349.824</v>
       </c>
       <c r="K9" t="n">
-        <v>3.999999999999998</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>288</v>
+        <v>277.4</v>
       </c>
       <c r="B10" t="n">
-        <v>132.6</v>
+        <v>139.3</v>
       </c>
       <c r="C10" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="E10" t="n">
-        <v>12254.04905141553</v>
+        <v>12068.17666109237</v>
       </c>
       <c r="F10" t="n">
-        <v>618.1174168234284</v>
+        <v>875.0687869041349</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>12319.61009694212</v>
+        <v>12125.58858622278</v>
       </c>
       <c r="I10" t="n">
-        <v>416.3412663262485</v>
+        <v>433.0214495602484</v>
       </c>
       <c r="J10" t="n">
-        <v>1387.456</v>
+        <v>1349.824</v>
       </c>
       <c r="K10" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>296</v>
+        <v>277.4</v>
       </c>
       <c r="B11" t="n">
-        <v>135.6</v>
+        <v>140</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>12475.54502003679</v>
+        <v>12072.12553408344</v>
       </c>
       <c r="F11" t="n">
-        <v>424.9882185746636</v>
+        <v>844.6641490654694</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>12475.54502003679</v>
+        <v>12126.21968464601</v>
       </c>
       <c r="I11" t="n">
-        <v>424.9882185746636</v>
+        <v>428.1622608645714</v>
       </c>
       <c r="J11" t="n">
-        <v>1400</v>
+        <v>1355.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.900000000000002</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
